--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -1,25 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5823554B-9116-44DC-9A82-C11ABF30865A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
+    <sheet name="respostas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>propietario</t>
   </si>
@@ -130,12 +143,21 @@
   </si>
   <si>
     <t>posssui memorial descritivo</t>
+  </si>
+  <si>
+    <t>respostas memorial descritivo</t>
+  </si>
+  <si>
+    <t>sim</t>
+  </si>
+  <si>
+    <t>não</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
@@ -148,12 +170,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -238,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -246,9 +274,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -257,19 +284,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,18 +574,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="51.5703125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="51.5703125" style="8" customWidth="1"/>
     <col min="5" max="5" width="26.7109375" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="9"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
     </row>
@@ -568,7 +592,7 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="3"/>
@@ -583,7 +607,7 @@
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="3"/>
@@ -599,7 +623,7 @@
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="13">
         <v>38323</v>
       </c>
     </row>
@@ -607,10 +631,10 @@
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -621,13 +645,13 @@
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>43822</v>
       </c>
     </row>
@@ -636,13 +660,13 @@
       <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>42911</v>
       </c>
     </row>
@@ -650,7 +674,7 @@
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="9">
         <v>1456.6547</v>
       </c>
     </row>
@@ -658,7 +682,7 @@
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -666,7 +690,7 @@
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="9">
         <v>1234.5123000000001</v>
       </c>
     </row>
@@ -674,7 +698,7 @@
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>156.65</v>
       </c>
     </row>
@@ -682,7 +706,7 @@
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="12">
         <v>25000000</v>
       </c>
     </row>
@@ -690,7 +714,7 @@
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="12">
         <v>65000000</v>
       </c>
     </row>
@@ -698,7 +722,7 @@
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -706,7 +730,7 @@
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="E16" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -714,7 +738,7 @@
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>100.5205</v>
       </c>
     </row>
@@ -722,7 +746,7 @@
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>321.56479999999999</v>
       </c>
     </row>
@@ -730,7 +754,7 @@
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -738,34 +762,75 @@
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>123456</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="15" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C6"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18"/>
+  <dataValidations count="5">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3 C6" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{45EB2A3C-C4B9-495C-9834-6A4579AC22F0}">
+          <x14:formula1>
+            <xm:f>respostas!$A$2:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C22</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A167AD16-3601-4C82-B56B-4E25BCBD2EA7}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5823554B-9116-44DC-9A82-C11ABF30865A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E9807C-36E5-4401-B181-C0D732707526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>propietario</t>
   </si>
@@ -142,16 +142,22 @@
     <t>fluid</t>
   </si>
   <si>
-    <t>posssui memorial descritivo</t>
-  </si>
-  <si>
     <t>respostas memorial descritivo</t>
   </si>
   <si>
-    <t>sim</t>
-  </si>
-  <si>
-    <t>não</t>
+    <t>georeferenciamento</t>
+  </si>
+  <si>
+    <t>CAR</t>
+  </si>
+  <si>
+    <t>Memorial descritivo</t>
+  </si>
+  <si>
+    <t>GEL</t>
+  </si>
+  <si>
+    <t>CAR e Memorial</t>
   </si>
 </sst>
 </file>
@@ -730,7 +736,7 @@
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -776,10 +782,10 @@
     </row>
     <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +803,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{45EB2A3C-C4B9-495C-9834-6A4579AC22F0}">
           <x14:formula1>
-            <xm:f>respostas!$A$2:$A$3</xm:f>
+            <xm:f>respostas!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>C22</xm:sqref>
         </x14:dataValidation>
@@ -809,7 +815,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A167AD16-3601-4C82-B56B-4E25BCBD2EA7}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -817,12 +823,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -830,7 +836,18 @@
         <v>39</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E9807C-36E5-4401-B181-C0D732707526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
     <sheet name="respostas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>propietario</t>
   </si>
@@ -158,12 +157,42 @@
   </si>
   <si>
     <t>CAR e Memorial</t>
+  </si>
+  <si>
+    <t>genero do propietario</t>
+  </si>
+  <si>
+    <t>empresa</t>
+  </si>
+  <si>
+    <t>Sr.</t>
+  </si>
+  <si>
+    <t>Sra.</t>
+  </si>
+  <si>
+    <t>hipotecas pendentes</t>
+  </si>
+  <si>
+    <t>sim</t>
+  </si>
+  <si>
+    <t>não</t>
+  </si>
+  <si>
+    <t>possuir hipotecas pendentes?</t>
+  </si>
+  <si>
+    <t>dentro do bioma amazonico?</t>
+  </si>
+  <si>
+    <t>inserido no bioma amazonico?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
@@ -190,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -268,11 +297,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -301,6 +343,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,11 +627,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
     <col min="3" max="3" width="51.5703125" style="8" customWidth="1"/>
     <col min="5" max="5" width="26.7109375" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
@@ -683,6 +730,12 @@
       <c r="C9" s="9">
         <v>1456.6547</v>
       </c>
+      <c r="E9" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -788,24 +841,58 @@
         <v>41</v>
       </c>
     </row>
+    <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3 C6" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+  <dataValidations xWindow="919" yWindow="330" count="5">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3 C6"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5 F3"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{45EB2A3C-C4B9-495C-9834-6A4579AC22F0}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="919" yWindow="330" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>respostas!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>C22</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>respostas!$B$2:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="por favor selecione algum valor da lista _x000a_༼ つ ಥ_ಥ ༽つ">
+          <x14:formula1>
+            <xm:f>respostas!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="validação de resposta" error="por favor selecione algum valor da lista">
+          <x14:formula1>
+            <xm:f>respostas!$D$2:$D$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -814,34 +901,67 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A167AD16-3601-4C82-B56B-4E25BCBD2EA7}">
-  <dimension ref="A1:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>41</v>
       </c>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="EstaPasta_de_trabalho" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>propietario</t>
   </si>
@@ -111,9 +111,6 @@
     <t>miguel phelipe feitosa</t>
   </si>
   <si>
-    <t>75.840.817/0001-77</t>
-  </si>
-  <si>
     <t>fazenda rancho diamante</t>
   </si>
   <si>
@@ -187,6 +184,21 @@
   </si>
   <si>
     <t>inserido no bioma amazonico?</t>
+  </si>
+  <si>
+    <t>11.111.111/1111-78</t>
+  </si>
+  <si>
+    <t>casado(a)</t>
+  </si>
+  <si>
+    <t>genero</t>
+  </si>
+  <si>
+    <t>nome</t>
+  </si>
+  <si>
+    <t>cpf</t>
   </si>
 </sst>
 </file>
@@ -219,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -310,11 +322,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -332,9 +368,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -346,6 +379,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -628,12 +668,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Planilha1"/>
   <dimension ref="B1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.42578125" customWidth="1"/>
     <col min="3" max="3" width="51.5703125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -668,7 +709,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -676,7 +717,7 @@
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>38323</v>
       </c>
     </row>
@@ -691,15 +732,15 @@
         <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>26</v>
+      <c r="C6" s="22" t="s">
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>24</v>
@@ -714,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>22</v>
@@ -730,11 +771,11 @@
       <c r="C9" s="9">
         <v>1456.6547</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>43</v>
+      <c r="E9" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -742,7 +783,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -752,6 +799,12 @@
       <c r="C11" s="9">
         <v>1234.5123000000001</v>
       </c>
+      <c r="E11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -760,20 +813,28 @@
       <c r="C12" s="9">
         <v>156.65</v>
       </c>
+      <c r="E12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="15"/>
     </row>
     <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>25000000</v>
       </c>
+      <c r="E13" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>65000000</v>
       </c>
     </row>
@@ -782,7 +843,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -790,7 +851,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -814,7 +875,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -822,12 +883,12 @@
         <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="9">
         <v>123456</v>
@@ -835,41 +896,42 @@
     </row>
     <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C24" s="17" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>48</v>
-      </c>
-    </row>
   </sheetData>
-  <dataValidations xWindow="919" yWindow="330" count="5">
+  <dataValidations xWindow="919" yWindow="330" count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3 C6"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5 F3"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="não precisa responder esses dados se não for casado(a)" sqref="F12 F13"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="919" yWindow="330" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="919" yWindow="330" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>respostas!$A$2:$A$5</xm:f>
@@ -894,6 +956,18 @@
           </x14:formula1>
           <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="validação de resultados" error="por favor escolha uma das opções da lista">
+          <x14:formula1>
+            <xm:f>respostas!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F10</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="por favor selecione algum valor da lista_x000a_" prompt="não precisa responder esses dados se não for casado(a)">
+          <x14:formula1>
+            <xm:f>respostas!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F11</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -902,6 +976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -912,58 +987,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>51</v>
+      <c r="A1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t>propietario</t>
   </si>
@@ -186,9 +186,6 @@
     <t>inserido no bioma amazonico?</t>
   </si>
   <si>
-    <t>11.111.111/1111-78</t>
-  </si>
-  <si>
     <t>casado(a)</t>
   </si>
   <si>
@@ -199,6 +196,18 @@
   </si>
   <si>
     <t>cpf</t>
+  </si>
+  <si>
+    <t>32.251.489/5614-55</t>
+  </si>
+  <si>
+    <t>bacia</t>
+  </si>
+  <si>
+    <t>sub-bacia</t>
+  </si>
+  <si>
+    <t>Rio tocantins</t>
   </si>
 </sst>
 </file>
@@ -669,7 +678,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="B1:F24"/>
+  <dimension ref="B1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.42578125" customWidth="1"/>
@@ -702,7 +711,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="6" t="s">
@@ -740,7 +749,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>24</v>
@@ -775,7 +784,7 @@
         <v>41</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -786,7 +795,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>47</v>
@@ -800,7 +809,7 @@
         <v>1234.5123000000001</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>43</v>
@@ -814,7 +823,7 @@
         <v>156.65</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="15"/>
     </row>
@@ -826,7 +835,7 @@
         <v>25000000</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -918,14 +927,29 @@
         <v>47</v>
       </c>
     </row>
+    <row r="25" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="10"/>
+    </row>
   </sheetData>
-  <dataValidations xWindow="919" yWindow="330" count="6">
+  <dataValidations xWindow="919" yWindow="330" count="7">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3 C6"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5 F3"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="não precisa responder esses dados se não for casado(a)" sqref="F12 F13"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="se não houver sub-bacia voce pode deixar em branco mesmo" sqref="C26"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
     <sheet name="respostas" sheetId="2" r:id="rId2"/>
+    <sheet name="DECLIVIDADE E PEDOLOGIA" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="114">
   <si>
     <t>propietario</t>
   </si>
@@ -129,9 +130,6 @@
     <t>TO</t>
   </si>
   <si>
-    <t>porto nacional</t>
-  </si>
-  <si>
     <t>palmas - to</t>
   </si>
   <si>
@@ -208,6 +206,240 @@
   </si>
   <si>
     <t>Rio tocantins</t>
+  </si>
+  <si>
+    <t>Constituída por áreas íngremes de regiões montanhosas, onde nenhum tipo de máquina agrícola pode trafegar. O escoamento superficial é sempre muito rápido e os solos extremamente suscetíveis à erosão hídrica.</t>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - (declive maior do que 45 %):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - (declive maior do que 30 % e igual ou menor do que 45 %):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - (declive maior do que 15 % e igual ou menor do que 30 %):</t>
+    </r>
+  </si>
+  <si>
+    <t>Compreende áreas inclinadas ou colinosas, onde o escoamento superficial é rápido na maior parte dos solos. A não ser que o declive seja muito complexo, a maior parte das máquinas agrícolas pode ser usada.</t>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - (declive maior do que 10 % e igual ou menor do que 15 %):</t>
+    </r>
+  </si>
+  <si>
+    <t>Áreas com superfícies inclinadas, geralmente com relevo ondulado, nos quais o escoamento superficial, para a maior parte dos solos, é médio ou rápido. O declive, por si só, normalmente não prejudica o uso de máquinas agrícolas.</t>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - (declive maior do que 5 % e igual ou menor do que 10 %):</t>
+    </r>
+  </si>
+  <si>
+    <t>Compreende áreas com declives suaves, nos quais, na maior parte dos solos, o escoamento superficial é lento ou médio. O declive, por si só, não impede ou dificulta o trabalho de qualquer tipo de máquina agrícola mais usual.</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - (declive igual ou inferior a 5 %):</t>
+    </r>
+  </si>
+  <si>
+    <t>DESCRIÇÃO</t>
+  </si>
+  <si>
+    <t>DECLIVIDADE</t>
+  </si>
+  <si>
+    <t>Plintossolo Argilúvico (FT)</t>
+  </si>
+  <si>
+    <t>Em geral, esses solos ocorrem em terço inferior de vertente e planícies, em posições que impliquem escoamento lento, alagamento temporário ou movimento interno da água no solo. Constituem solos com restrições à penetração de água e raízes.</t>
+  </si>
+  <si>
+    <t>Plintossolos Háplico (FX)</t>
+  </si>
+  <si>
+    <t>Os plintossolos pétricos são os solos de maior predominância. São usados para pastoreio extensivo nas áreas de vegetação campestre ou de Campo Cerrado, ou com pasto plantado com espécies forrageiras rústicas.</t>
+  </si>
+  <si>
+    <t>Plintossolos Pétrico (FF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possuem a característica de serem bem abastecidos de bases, o que lhes confere elevado status nutricional, mas com sérias limitações de ordem física relacionadas principalmente ao preparo do solo e à penetração de raízes devido ao adensamento. </t>
+  </si>
+  <si>
+    <t>Planossolos Háplicos (SX)</t>
+  </si>
+  <si>
+    <t>Planossolos Nátricos (SN)</t>
+  </si>
+  <si>
+    <t>Os Nitossolos Vermelhos compreendem solos constituídos por material mineral, com horizonte B nítico de argila de atividade baixa, profundo e muito profundo, bem drenado, baixo gradiente textural e com estruturas em blocos e cerosidade bem desenvolvidas.</t>
+  </si>
+  <si>
+    <t>Nitossolo Vermelho (NV)</t>
+  </si>
+  <si>
+    <t>Solos rasos e jovens, geralmente associados a regiões de relevo acidentado ou rochoso. Possuem baixo desenvolvimento do perfil pedológico, com o material de origem próximo à superfície.</t>
+  </si>
+  <si>
+    <t>Neossolos Litólicos (RL)</t>
+  </si>
+  <si>
+    <t>Neossolos Quartzarênicos (RQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os Neossolos Flúvicos, correspondentes aos solos aluviais na classificação anteriormente adotada no Brasil, compreendem solos pouco evoluídos, não hidromórficos, formados preferencialmente em terraços de deposição aluvionar. </t>
+  </si>
+  <si>
+    <t>Neossolo flúvico (RY)</t>
+  </si>
+  <si>
+    <t>Luvissolos Háplicos (TX)</t>
+  </si>
+  <si>
+    <t>Compreendem solos com horizonte B latossólico imediatamente abaixo do horizonte A, nesse caso, moderado. São solos em avançado estágio de intemperização, muito evoluídos, como resultado de enérgicas transformações no material constitutivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latossolo Vermelho (LV) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latossolo Amarelo (LA) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latossolo Vermelho-Amarelo (LVA) </t>
+  </si>
+  <si>
+    <t>Solos característicos de áreas com excesso de água, como várzeas e terrenos alagáveis. Possuem cores acinzentadas ou azuladas devido à saturação hídrica e baixa oxigenação, o que limita seu uso agrícola sem drenagem adequada.</t>
+  </si>
+  <si>
+    <t>Gleissolo háplico (GX)</t>
+  </si>
+  <si>
+    <t>Solos ricos em matéria orgânica, comuns em regiões de clima mais frio ou subúmido. Caracterizam-se pela alta fertilidade natural devido ao elevado teor de bases e pela presença de horizonte A chernozêmico.</t>
+  </si>
+  <si>
+    <t>Chernossolo Argilúvico (MT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São solos constituídos por material mineral, com horizonte B. Devido à heterogeneidade do material de origem, das formas de relevo e das condições climáticas, as características destes solos variam muito de um local para outro. </t>
+  </si>
+  <si>
+    <t>Cambissolos (CX)</t>
+  </si>
+  <si>
+    <t>Engloba solos minerais não hidromórficos. São profundos e muito profundos; bem estruturados e bem drenados, com argila de atividade baixa, horizonte A do tipo moderado e texturas média/argilosa e arenosa/média.</t>
+  </si>
+  <si>
+    <t>Argissolo vermelho-amarelo (PVA)</t>
+  </si>
+  <si>
+    <t>Solos com horizonte B textural, caracterizados por cores avermelhadas devido à alta concentração de óxidos de ferro. São bem drenados, porém ácidos e de fertilidade moderada a baixa.</t>
+  </si>
+  <si>
+    <t>Argissolo Vermelho (PV)</t>
+  </si>
+  <si>
+    <t>Argissolo Amarelo (PA)</t>
+  </si>
+  <si>
+    <t>Os afloramentos rochosos são elevações monolíticas ou agrupadas que aparecem isoladas na paisagem circundante. Embora sejam encontrados sob os mais variados domínios climáticos, são mais abundantes em regiões tropicais e subtropicais.</t>
+  </si>
+  <si>
+    <t>Afloramento Rochosos (AR)</t>
+  </si>
+  <si>
+    <t>PEDOLOGIA</t>
+  </si>
+  <si>
+    <t>Representada por áreas inclinadas, cujo escoamento superficial é rápido a muito rápido na maior parte dos solos. Podem ser trabalhados mecanicamente apenas em curvas de nível por máquinas simples de tração animal.</t>
+  </si>
+  <si>
+    <t>Áreas fortemente inclinadas, cujo escoamento superficial é muito rápido. Podem ser trabalhados mecanicamente somente por máquinas simples de tração animal, assim mesmo com sérias limitações.</t>
+  </si>
+  <si>
+    <t>Essa classe é constituída por solos minerais não hidromórficos, bem intemperizados, bastante evoluídos, bem drenados, profundos, com argila de atividade baixa e horizonte B textural formado pela acumulação de argila com sequência de horizontes A, Bt e C.</t>
+  </si>
+  <si>
+    <t>Solos profundos e bem drenados, predominantes em regiões tropicais. Apresentam cores avermelhadas a amareladas devido à presença de óxidos de ferro. Embora sejam ácidos e de baixa fertilidade natural, podem ser corrigidos e utilizados intensivamente na agricultura.</t>
+  </si>
+  <si>
+    <t>Em geral, os Latossolos são macios, de consistência úmida friável ou muito friável por todo o perfil. Comumente, são muito profundos, atingindo vários metros de espessura e apresentando homogeneidade vertical com relação a vários atributos morfológicos.</t>
+  </si>
+  <si>
+    <t>Apresenta o caráter eutrófico, assim, a alta saturação por bases nos horizontes subsuperficiais, o que favorece o enraizamento em profundidade. Outro aspecto refere-se à presença de minerais primários facilmente intemperizáveis.</t>
+  </si>
+  <si>
+    <t>Solos sem contato lítico dentro de 50cm de profundidade, com sequência de horizontes A-C, porém apresentando textura areia ou areia franca em todos os horizontes até, no mínimo, a profundidade de 150 cm a partir da superfície do solo ou até contato lítico.</t>
+  </si>
+  <si>
+    <t>Os Planossolos Nátricos possuem alta saturação por sódio, estrutura prismática ou colunar. O gradiente textural elevado causa grande suscetibilidade à erosão, também favorecida pela baixa permeabilidade do horizonte B, devido à alta concentração de sódio.</t>
+  </si>
+  <si>
+    <t>Solos com presença de plintita, uma formação rica em ferro e alumínio que endurece quando exposta à seca ou à drenagem deficiente. Esses solos têm baixa fertilidade e são encontrados em áreas com oscilação de umidade.</t>
+  </si>
+  <si>
+    <t>porto nacional - TO</t>
   </si>
 </sst>
 </file>
@@ -217,7 +449,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,8 +457,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,8 +503,134 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -355,18 +745,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -386,17 +800,58 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,281 +1137,284 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.5703125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="51.5703125" style="6" customWidth="1"/>
     <col min="5" max="5" width="31.28515625" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="6" t="s">
+      <c r="C3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="2"/>
+      <c r="E4" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="10">
+        <v>38323</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="3"/>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="12">
-        <v>38323</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>43822</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>42911</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>1456.6547</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="20" t="s">
+    </row>
+    <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1234.5123000000001</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="55" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="18" t="s">
+    <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7">
+        <v>156.65</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="9">
+        <v>25000000</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="9">
+        <v>65000000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7">
+        <v>100.5205</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="7">
+        <v>321.56479999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="7">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="29" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="9">
-        <v>1234.5123000000001</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="9">
-        <v>156.65</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="15"/>
-    </row>
-    <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="11">
-        <v>25000000</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="11">
-        <v>65000000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="9">
-        <v>100.5205</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="9">
-        <v>321.56479999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="9">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="16" t="s">
+      <c r="C23" s="45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C24" s="46" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
     <row r="25" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="8"/>
     </row>
   </sheetData>
-  <dataValidations xWindow="919" yWindow="330" count="7">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo" sqref="C20"/>
+  <dataValidations xWindow="919" yWindow="330" count="10">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo _x000a_|(◕‿◕)|" sqref="C20"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3 C6"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj (◎_◎;)_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C6"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5 F3"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS" sqref="C11 C17 C18"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS _x000a_⊂(◉‿◉)つ" sqref="C18"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="não precisa responder esses dados se não for casado(a)" sqref="F12 F13"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="se não houver sub-bacia voce pode deixar em branco mesmo" sqref="C26"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="se não houver sub-bacia voce pode deixar em branco mesmo_x000a_༼ つ ◕_◕ ༽つ" sqref="C26"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj ಠ‿ಠ_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS ୧༼ಠ益ಠ༽୨" sqref="C11"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS   _x000a_ヽ༼ ಠ益ಠ ༽ﾉ" sqref="C17"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="919" yWindow="330" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="por favor selecione algum valor da lista_x000a_ᕦ(✧╭╮✧)ᕥ">
           <x14:formula1>
             <xm:f>respostas!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -974,7 +1432,7 @@
           </x14:formula1>
           <xm:sqref>C23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="validação de resposta" error="por favor selecione algum valor da lista">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="validação de resposta" error="por favor selecione algum valor da lista" prompt="por favor selecione algum valor da lista _x000a_ʕ⊙ᴥ⊙ʔ">
           <x14:formula1>
             <xm:f>respostas!$D$2:$D$3</xm:f>
           </x14:formula1>
@@ -1011,62 +1469,302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>50</v>
+      <c r="A1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="61" customWidth="1"/>
+    <col min="3" max="3" width="90.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -1397,30 +1397,35 @@
       <c r="C26" s="8"/>
     </row>
   </sheetData>
-  <dataValidations xWindow="919" yWindow="330" count="10">
+  <dataValidations xWindow="461" yWindow="491" count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="utilize apenas 2 letras e deixe-as maiusculo _x000a_|(◕‿◕)|" sqref="C20"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000" sqref="F8 F6 F4"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000_x000a_(つ☯ᗜ☯)つ" sqref="F8"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj (◎_◎;)_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C6"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : cidade - uf" sqref="F5 F3"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado :_x000a_CIDADE - UF_x000a_(づ｡◕‿‿◕｡)づ" sqref="F5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS _x000a_⊂(◉‿◉)つ" sqref="C18"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="não precisa responder esses dados se não for casado(a)" sqref="F12 F13"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="não precisa responder esses dados se não for casado(a)_x000a__x000a_ლ(̿▀̿ ̿Ĺ̯̿̿▀̿ ̿ლ)" sqref="F13"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="se não houver sub-bacia voce pode deixar em branco mesmo_x000a_༼ つ ◕_◕ ༽つ" sqref="C26"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj ಠ‿ಠ_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="C3"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS ୧༼ಠ益ಠ༽୨" sqref="C11"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS   _x000a_ヽ༼ ಠ益ಠ ༽ﾉ" sqref="C17"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formatado com estado : _x000a_CIDADE - UF_x000a_ヽ༼ಢ_ಢ༽ﾉ☂" sqref="F3"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000_x000a_(づ°‿°.)づ" sqref="F4"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formato 00/00/0000_x000a_ヽ༼ ʘ ∧ ʘ ༽ᓄ" sqref="F6"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="NESTE CAMPO VOCE UTILIZE VIRGULAS E NÃO PONTOS'(◣_◢)'" sqref="C12"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="não precisa responder esses dados se não for casado(a)_x000a_⊂(♀σ♀)つ" sqref="F12"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="919" yWindow="330" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="461" yWindow="491" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="por favor selecione algum valor da lista_x000a_ᕦ(✧╭╮✧)ᕥ">
           <x14:formula1>
             <xm:f>respostas!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>C22</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="por favor selecione algum valor da lista_x000a_( ͡°( ͡° ͜ʖ( ͡° ͜ʖ ͡°)ʖ ͡°) ͡°)">
           <x14:formula1>
             <xm:f>respostas!$B$2:$B$4</xm:f>
           </x14:formula1>
@@ -1438,13 +1443,13 @@
           </x14:formula1>
           <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="validação de resultados" error="por favor escolha uma das opções da lista">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="validação de resultados" error="por favor escolha uma das opções da lista" prompt="por favor selecione algum valor da lista_x000a_٩(×̯×)۶">
           <x14:formula1>
             <xm:f>respostas!$C$2:$C$3</xm:f>
           </x14:formula1>
           <xm:sqref>F10</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="por favor selecione algum valor da lista_x000a_" prompt="não precisa responder esses dados se não for casado(a)">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="por favor selecione algum valor da lista_x000a_" prompt="não precisa responder esses dados se não for casado(a)_x000a_༼ﾉ۞⌂۞༽ﾉ">
           <x14:formula1>
             <xm:f>respostas!$B$2:$B$3</xm:f>
           </x14:formula1>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -9,26 +9,24 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
-    <sheet name="valores" sheetId="3" r:id="rId2"/>
-    <sheet name="propietarios" sheetId="2" r:id="rId3"/>
-    <sheet name="imovel" sheetId="4" r:id="rId4"/>
-    <sheet name="quadro_resumo" sheetId="5" r:id="rId5"/>
-    <sheet name="DECLIVIDADE E PEDOLOGIA" sheetId="6" r:id="rId6"/>
-    <sheet name="respostas" sheetId="7" r:id="rId7"/>
+    <sheet name="propietarios" sheetId="2" r:id="rId2"/>
+    <sheet name="quadro_resumo" sheetId="3" r:id="rId3"/>
+    <sheet name="DECLIVIDADE E PEDOLOGIA" sheetId="4" r:id="rId4"/>
+    <sheet name="respostas" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_Hlk173855386" localSheetId="4">quadro_resumo!$A$1</definedName>
+    <definedName name="_Hlk173855386" localSheetId="2">quadro_resumo!$A$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="154">
   <si>
     <t>proponente</t>
   </si>
@@ -54,132 +52,132 @@
     <t>porto nacional - TO</t>
   </si>
   <si>
-    <t>proponente e propietario iguais?</t>
+    <t>mais de um propietario?</t>
+  </si>
+  <si>
+    <t>data de solicitação</t>
+  </si>
+  <si>
+    <t>propietario</t>
+  </si>
+  <si>
+    <t>miguel phelipe feitosa</t>
+  </si>
+  <si>
+    <t>municipio do cartorio</t>
+  </si>
+  <si>
+    <t>palmas - to</t>
+  </si>
+  <si>
+    <t>713.254.791-79</t>
+  </si>
+  <si>
+    <t>data de emissão do cartorio</t>
+  </si>
+  <si>
+    <t>mais de uma matricula?</t>
+  </si>
+  <si>
+    <t>nome do imovel</t>
+  </si>
+  <si>
+    <t>fazenda rancho diamante</t>
+  </si>
+  <si>
+    <t>data da vistoria</t>
+  </si>
+  <si>
+    <t>matricula</t>
+  </si>
+  <si>
+    <t>genero do propietario</t>
+  </si>
+  <si>
+    <t>empresa</t>
+  </si>
+  <si>
+    <t>identificação</t>
+  </si>
+  <si>
+    <t>fazenda</t>
+  </si>
+  <si>
+    <t>casado(a)</t>
+  </si>
+  <si>
+    <t>não</t>
+  </si>
+  <si>
+    <t>area há</t>
+  </si>
+  <si>
+    <t>genero</t>
+  </si>
+  <si>
+    <t>Sr.</t>
+  </si>
+  <si>
+    <t>area construida</t>
+  </si>
+  <si>
+    <t>nome</t>
+  </si>
+  <si>
+    <t>valor de mercado</t>
+  </si>
+  <si>
+    <t>cpf</t>
+  </si>
+  <si>
+    <t>liquidação forçada</t>
+  </si>
+  <si>
+    <t>car</t>
+  </si>
+  <si>
+    <t>TO-1718204-E7A1.2B1B.6B15.4E03.89DD.7006.7298.400E</t>
+  </si>
+  <si>
+    <t>gel</t>
+  </si>
+  <si>
+    <t>c8bdfa60-64a7-4baa-83aa-d84b73759e3e</t>
+  </si>
+  <si>
+    <t>area1</t>
+  </si>
+  <si>
+    <t>area2</t>
+  </si>
+  <si>
+    <t>municipio</t>
+  </si>
+  <si>
+    <t>palmas</t>
+  </si>
+  <si>
+    <t>estado(uf)</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>fluid</t>
+  </si>
+  <si>
+    <t>georeferenciamento</t>
+  </si>
+  <si>
+    <t>CAR e Memorial</t>
+  </si>
+  <si>
+    <t>possui hipotecas pendentes?</t>
   </si>
   <si>
     <t>sim</t>
   </si>
   <si>
-    <t>data de solicitação</t>
-  </si>
-  <si>
-    <t>propietario</t>
-  </si>
-  <si>
-    <t>miguel phelipe feitosa</t>
-  </si>
-  <si>
-    <t>municipio do cartorio</t>
-  </si>
-  <si>
-    <t>palmas - to</t>
-  </si>
-  <si>
-    <t>713.254.791-79</t>
-  </si>
-  <si>
-    <t>data de emissão do cartorio</t>
-  </si>
-  <si>
-    <t>mais de um propietario?</t>
-  </si>
-  <si>
-    <t>nome do imovel</t>
-  </si>
-  <si>
-    <t>fazenda rancho diamante</t>
-  </si>
-  <si>
-    <t>data da vistoria</t>
-  </si>
-  <si>
-    <t>matricula</t>
-  </si>
-  <si>
-    <t>genero do propietario</t>
-  </si>
-  <si>
-    <t>empresa</t>
-  </si>
-  <si>
-    <t>identificação</t>
-  </si>
-  <si>
-    <t>fazenda</t>
-  </si>
-  <si>
-    <t>casado(a)</t>
-  </si>
-  <si>
-    <t>não</t>
-  </si>
-  <si>
-    <t>area há</t>
-  </si>
-  <si>
-    <t>genero</t>
-  </si>
-  <si>
-    <t>Sr.</t>
-  </si>
-  <si>
-    <t>area construida</t>
-  </si>
-  <si>
-    <t>nome</t>
-  </si>
-  <si>
-    <t>valor de mercado</t>
-  </si>
-  <si>
-    <t>cpf</t>
-  </si>
-  <si>
-    <t>liquidação forçada</t>
-  </si>
-  <si>
-    <t>car</t>
-  </si>
-  <si>
-    <t>TO-1718204-E7A1.2B1B.6B15.4E03.89DD.7006.7298.400E</t>
-  </si>
-  <si>
-    <t>gel</t>
-  </si>
-  <si>
-    <t>c8bdfa60-64a7-4baa-83aa-d84b73759e3e</t>
-  </si>
-  <si>
-    <t>area1</t>
-  </si>
-  <si>
-    <t>area2</t>
-  </si>
-  <si>
-    <t>municipio</t>
-  </si>
-  <si>
-    <t>palmas</t>
-  </si>
-  <si>
-    <t>estado(uf)</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>fluid</t>
-  </si>
-  <si>
-    <t>georeferenciamento</t>
-  </si>
-  <si>
-    <t>CAR e Memorial</t>
-  </si>
-  <si>
-    <t>possuir hipotecas pendentes?</t>
-  </si>
-  <si>
     <t>dentro do bioma amazonico?</t>
   </si>
   <si>
@@ -219,6 +217,9 @@
     <t>liquidação</t>
   </si>
   <si>
+    <t>CODIGO GEL</t>
+  </si>
+  <si>
     <t>propietario 1</t>
   </si>
   <si>
@@ -294,46 +295,13 @@
     <t>matricula10</t>
   </si>
   <si>
-    <t>IMÓVEL</t>
-  </si>
-  <si>
-    <t>Nº Matrícula</t>
-  </si>
-  <si>
-    <t>Valor de mercado</t>
-  </si>
-  <si>
-    <t>Liquidação forçada</t>
-  </si>
-  <si>
-    <t>Identificação</t>
-  </si>
-  <si>
-    <t>Área há</t>
-  </si>
-  <si>
-    <t>Área Construída m²</t>
-  </si>
-  <si>
     <t>QUADRO RESUMO DA AVALIAÇÃO</t>
   </si>
   <si>
-    <t>Agencia:</t>
-  </si>
-  <si>
-    <t>#agencia</t>
-  </si>
-  <si>
     <t>Proponente:</t>
   </si>
   <si>
-    <t>#486: 513.254.791-79</t>
-  </si>
-  <si>
-    <t>Identificação:</t>
-  </si>
-  <si>
-    <t>#nome_imovel</t>
+    <t xml:space="preserve">#486: </t>
   </si>
   <si>
     <t>DECLIVIDADE</t>
@@ -529,7 +497,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,8 +557,15 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -699,12 +674,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -902,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -985,47 +954,27 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1352,15 +1301,13 @@
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="1"/>
       <c r="E4" s="33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="8">
         <v>38323</v>
@@ -1368,16 +1315,16 @@
     </row>
     <row r="5" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="F5" s="56" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1385,30 +1332,30 @@
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>16</v>
       </c>
       <c r="F6" s="4">
         <v>43822</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="50" t="s">
-        <v>17</v>
+      <c r="B7" s="62" t="s">
+        <v>16</v>
       </c>
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="E8" s="27" t="s">
         <v>19</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>20</v>
       </c>
       <c r="F8" s="4">
         <v>42911</v>
@@ -1416,73 +1363,73 @@
     </row>
     <row r="9" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5">
         <v>1456.6547</v>
       </c>
       <c r="E9" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="38" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="E10" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="F10" s="37" t="s">
         <v>26</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="5">
         <v>1234.5123000000001</v>
       </c>
       <c r="E11" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="39" t="s">
         <v>29</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5">
         <v>156.65</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" s="54"/>
     </row>
     <row r="13" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="7">
         <v>25000000</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="7">
         <v>65000000</v>
@@ -1490,23 +1437,23 @@
     </row>
     <row r="15" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="5">
         <v>100.5205</v>
@@ -1514,7 +1461,7 @@
     </row>
     <row r="18" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="5">
         <v>321.56479999999999</v>
@@ -1522,23 +1469,23 @@
     </row>
     <row r="19" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="5">
         <v>123456</v>
@@ -1546,18 +1493,18 @@
     </row>
     <row r="22" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>49</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1565,7 +1512,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1612,63 +1559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-    </row>
-    <row r="2" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="59"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L23"/>
+  <dimension ref="B1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" style="63" customWidth="1"/>
@@ -1679,95 +1570,93 @@
     <col min="7" max="8" width="18.7109375" style="63" customWidth="1"/>
     <col min="9" max="9" width="15.85546875" style="63" customWidth="1"/>
     <col min="10" max="10" width="20.5703125" style="63" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="63" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" style="63" customWidth="1"/>
+    <col min="11" max="12" width="18.140625" style="63" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" style="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="61" t="s">
+    <row r="1" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="62" t="s">
+      <c r="I2" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="62" t="s">
+      <c r="K2" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="62" t="s">
+      <c r="L2" s="60" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M2" s="60" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="56" t="str">
-        <f>dados!C5</f>
-        <v>miguel phelipe feitosa</v>
-      </c>
-      <c r="D3" s="55" t="str">
-        <f>dados!C6</f>
-        <v>713.254.791-79</v>
+        <v>64</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>14</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" s="56">
-        <f>dados!C9</f>
         <v>1456.6547</v>
       </c>
-      <c r="H3" s="56" t="str">
-        <f>dados!C10</f>
-        <v>fazenda</v>
+      <c r="H3" s="56" t="s">
+        <v>24</v>
       </c>
       <c r="I3" s="56">
-        <f>dados!C11</f>
         <v>1234.5123000000001</v>
       </c>
       <c r="J3" s="56">
-        <f>dados!C12</f>
         <v>156.65</v>
       </c>
-      <c r="K3" s="60">
-        <f>dados!C13</f>
+      <c r="K3" s="58">
         <v>25000000</v>
       </c>
-      <c r="L3" s="60">
-        <f>dados!C14</f>
+      <c r="L3" s="58">
         <v>65000000</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="47">
         <v>184.096</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="47">
         <v>123.0921</v>
@@ -1781,31 +1670,32 @@
       <c r="L4" s="47">
         <v>1000</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="47"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" s="47">
         <v>58744</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H5" s="47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J5" s="56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K5" s="56">
         <v>10000</v>
@@ -1813,15 +1703,16 @@
       <c r="L5" s="56">
         <v>20000</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="56"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="47"/>
       <c r="F6" s="57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="56"/>
       <c r="H6" s="56"/>
@@ -1829,15 +1720,16 @@
       <c r="J6" s="56"/>
       <c r="K6" s="56"/>
       <c r="L6" s="56"/>
-    </row>
-    <row r="7" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="56"/>
+    </row>
+    <row r="7" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="47"/>
       <c r="F7" s="57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="56"/>
       <c r="H7" s="56"/>
@@ -1845,15 +1737,16 @@
       <c r="J7" s="56"/>
       <c r="K7" s="56"/>
       <c r="L7" s="56"/>
-    </row>
-    <row r="8" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="56"/>
+    </row>
+    <row r="8" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="47"/>
       <c r="F8" s="57" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="56"/>
       <c r="H8" s="56"/>
@@ -1861,14 +1754,15 @@
       <c r="J8" s="56"/>
       <c r="K8" s="56"/>
       <c r="L8" s="56"/>
-    </row>
-    <row r="9" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="56"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" s="47"/>
       <c r="F9" s="57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" s="56"/>
       <c r="H9" s="56"/>
@@ -1876,15 +1770,16 @@
       <c r="J9" s="56"/>
       <c r="K9" s="56"/>
       <c r="L9" s="56"/>
-    </row>
-    <row r="10" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="56"/>
+    </row>
+    <row r="10" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="53"/>
       <c r="D10" s="47"/>
       <c r="F10" s="57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
@@ -1892,15 +1787,16 @@
       <c r="J10" s="56"/>
       <c r="K10" s="56"/>
       <c r="L10" s="56"/>
-    </row>
-    <row r="11" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="56"/>
+    </row>
+    <row r="11" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="51"/>
       <c r="D11" s="47"/>
       <c r="F11" s="57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" s="56"/>
       <c r="H11" s="56"/>
@@ -1908,15 +1804,16 @@
       <c r="J11" s="56"/>
       <c r="K11" s="56"/>
       <c r="L11" s="56"/>
-    </row>
-    <row r="12" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="56"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="53"/>
       <c r="D12" s="47"/>
       <c r="F12" s="57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
@@ -1924,18 +1821,79 @@
       <c r="J12" s="56"/>
       <c r="K12" s="56"/>
       <c r="L12" s="56"/>
-    </row>
-    <row r="13" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M12" s="56"/>
+    </row>
+    <row r="13" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="56" t="str">
+        <f>dados!F11</f>
+        <v>Sr.</v>
+      </c>
+      <c r="C15" s="56">
+        <f>dados!F12</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="56">
+        <f>dados!F13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+    </row>
+    <row r="17" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+    </row>
+    <row r="18" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+    </row>
+    <row r="19" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+    </row>
+    <row r="20" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+    </row>
+    <row r="21" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+    </row>
+    <row r="22" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+    </row>
+    <row r="23" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+    </row>
+    <row r="24" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj ಠ‿ಠ_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="D4"/>
@@ -1945,166 +1903,77 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="14" width="9.140625" style="64" customWidth="1"/>
+    <col min="1" max="63" width="9.140625" style="63" customWidth="1"/>
+    <col min="64" max="16384" width="9.140625" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="69" t="s">
-        <v>93</v>
-      </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="58"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+    </row>
+    <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="K2:N2"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="61" width="9.140625" style="63" customWidth="1"/>
-    <col min="62" max="16384" width="9.140625" style="63"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="71"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-    </row>
-    <row r="2" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="71" t="str">
-        <f>dados!C2</f>
-        <v>marco antonio feitosa</v>
-      </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="72" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="65" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q2" s="75" t="s">
-        <v>101</v>
-      </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="66"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="Q2:W2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2116,227 +1985,227 @@
     <row r="1" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="17" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="17" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="17" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2344,7 +2213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:D5"/>
@@ -2358,58 +2227,58 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,12 @@
   <definedNames>
     <definedName name="_Hlk173855386" localSheetId="2">quadro_resumo!$A$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="147">
   <si>
     <t>proponente</t>
   </si>
@@ -193,12 +193,18 @@
     <t>colocar valores que tem lista em primeiro</t>
   </si>
   <si>
+    <t>% imovel</t>
+  </si>
+  <si>
     <t>NOME</t>
   </si>
   <si>
     <t>cpf ou cnpj</t>
   </si>
   <si>
+    <t>casado?(a)</t>
+  </si>
+  <si>
     <t>Nº matricula</t>
   </si>
   <si>
@@ -220,22 +226,16 @@
     <t>CODIGO GEL</t>
   </si>
   <si>
-    <t>propietario 1</t>
-  </si>
-  <si>
     <t>matricula1</t>
   </si>
   <si>
-    <t>propietario 2</t>
-  </si>
-  <si>
     <t>miguel phelipe feitosa gomes</t>
   </si>
   <si>
     <t>matricula2</t>
   </si>
   <si>
-    <t>propietario 3</t>
+    <t>Sra.</t>
   </si>
   <si>
     <t>testando</t>
@@ -253,55 +253,37 @@
     <t>mara9-1</t>
   </si>
   <si>
-    <t>propietario 4</t>
-  </si>
-  <si>
     <t>matricula4</t>
   </si>
   <si>
-    <t>propietario 5</t>
-  </si>
-  <si>
     <t>matricula5</t>
   </si>
   <si>
-    <t>propietario 6</t>
-  </si>
-  <si>
     <t>matricula6</t>
   </si>
   <si>
-    <t>propietario 7</t>
-  </si>
-  <si>
     <t>matricula7</t>
   </si>
   <si>
-    <t>propietario 8</t>
-  </si>
-  <si>
     <t>matricula8</t>
   </si>
   <si>
-    <t>propietario 9</t>
-  </si>
-  <si>
     <t>matricula9</t>
   </si>
   <si>
-    <t>propietario 10</t>
-  </si>
-  <si>
     <t>matricula10</t>
   </si>
   <si>
+    <t>marco antonio</t>
+  </si>
+  <si>
     <t>QUADRO RESUMO DA AVALIAÇÃO</t>
   </si>
   <si>
     <t>Proponente:</t>
   </si>
   <si>
-    <t xml:space="preserve">#486: </t>
+    <t>#486: 32.251.489/5614-55</t>
   </si>
   <si>
     <t>DECLIVIDADE</t>
@@ -482,9 +464,6 @@
   </si>
   <si>
     <t>Memorial descritivo</t>
-  </si>
-  <si>
-    <t>Sra.</t>
   </si>
   <si>
     <t>CAR</t>
@@ -497,7 +476,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,13 +532,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
@@ -871,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -939,8 +911,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -951,30 +921,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1261,7 +1234,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.85546875" style="63" customWidth="1"/>
-    <col min="3" max="3" width="51.5703125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="51.5703125" style="50" customWidth="1"/>
     <col min="5" max="5" width="31.28515625" style="63" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" style="63" customWidth="1"/>
   </cols>
@@ -1281,12 +1254,12 @@
       <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="53" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="47" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1296,12 +1269,12 @@
       <c r="E3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="53" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="48" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="5"/>
@@ -1323,12 +1296,12 @@
       <c r="E5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="53" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="47" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -1342,7 +1315,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="57" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="5"/>
@@ -1413,7 +1386,7 @@
       <c r="E12" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="54"/>
+      <c r="F12" s="52"/>
     </row>
     <row r="13" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
@@ -1476,7 +1449,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="46" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -1559,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" style="63" customWidth="1"/>
@@ -1574,328 +1547,364 @@
     <col min="13" max="13" width="18.28515625" style="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="59" t="s">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="C2" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="D2" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="E2" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="G2" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="H2" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="I2" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="60" t="s">
+      <c r="J2" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="M2" s="60" t="s">
+      <c r="K2" s="56" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="2:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
+      <c r="L2" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="M2" s="56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="52">
+        <v>12</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="56">
+      <c r="E3" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="53">
         <v>1456.6547</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="53">
         <v>1234.5123000000001</v>
       </c>
-      <c r="J3" s="56">
+      <c r="J3" s="53">
         <v>156.65</v>
       </c>
-      <c r="K3" s="58">
+      <c r="K3" s="54">
         <v>25000000</v>
       </c>
-      <c r="L3" s="58">
+      <c r="L3" s="54">
         <v>65000000</v>
       </c>
-      <c r="M3" s="58" t="s">
+      <c r="M3" s="54" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="56" t="s">
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2">
+        <v>15</v>
+      </c>
+      <c r="C4" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="E4" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="45">
         <v>184.096</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="47">
+      <c r="I4" s="45">
         <v>123.0921</v>
       </c>
-      <c r="J4" s="47">
+      <c r="J4" s="45">
         <v>15.65</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="45">
         <v>100000</v>
       </c>
-      <c r="L4" s="47">
+      <c r="L4" s="45">
         <v>1000</v>
       </c>
-      <c r="M4" s="47"/>
-    </row>
-    <row r="5" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="47" t="s">
+      <c r="M4" s="45"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="53" t="s">
         <v>69</v>
+      </c>
+      <c r="B5" s="2">
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="44">
         <v>58744</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="E5" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="56" t="s">
+      <c r="G5" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="56" t="s">
+      <c r="I5" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="K5" s="56">
+      <c r="K5" s="53">
         <v>10000</v>
       </c>
-      <c r="L5" s="56">
+      <c r="L5" s="53">
         <v>20000</v>
       </c>
-      <c r="M5" s="56"/>
-    </row>
-    <row r="6" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="47" t="s">
+      <c r="M5" s="53"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="47"/>
-      <c r="F6" s="57" t="s">
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="53"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-    </row>
-    <row r="7" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="47" t="s">
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="53"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="47"/>
-      <c r="F7" s="57" t="s">
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="53"/>
+      <c r="B9" s="1"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-    </row>
-    <row r="8" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="47" t="s">
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="53"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="47"/>
-      <c r="F8" s="57" t="s">
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="53"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-    </row>
-    <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="53"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="F9" s="57" t="s">
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-    </row>
-    <row r="10" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="47"/>
-      <c r="F10" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-    </row>
-    <row r="11" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="47"/>
-      <c r="F11" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-    </row>
-    <row r="12" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="47"/>
-      <c r="F12" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-    </row>
-    <row r="13" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="59" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="56" t="str">
-        <f>dados!F11</f>
-        <v>Sr.</v>
-      </c>
-      <c r="C15" s="56">
-        <f>dados!F12</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="56">
-        <f>dados!F13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
+      <c r="D15" s="53">
+        <v>9874165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="53">
+        <v>9874165</v>
+      </c>
     </row>
     <row r="17" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
+      <c r="B17" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="53">
+        <v>9874165</v>
+      </c>
     </row>
     <row r="18" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
     </row>
     <row r="20" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
     </row>
     <row r="21" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
     </row>
     <row r="22" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
     </row>
     <row r="23" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-    </row>
-    <row r="24" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+    </row>
+    <row r="24" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="deixe no formata de cpf ou cnpj ಠ‿ಠ_x000a__x000a_000.000.000-00_x000a__x000a_00.000.000/0000-00" sqref="D4"/>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1908,65 +1917,61 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="63" width="9.140625" style="63" customWidth="1"/>
-    <col min="64" max="16384" width="9.140625" style="63"/>
+    <col min="1" max="69" width="9.140625" style="63" customWidth="1"/>
+    <col min="70" max="16384" width="9.140625" style="63"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
+      <c r="A1" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
     </row>
     <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="67" t="s">
+      <c r="A2" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="K2" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="O2" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="O1:S1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C2:I2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1985,227 +1990,227 @@
     <row r="1" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>93</v>
+      <c r="B13" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="17" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="17" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="17" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2227,21 +2232,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B1" s="41" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
@@ -2255,10 +2260,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
@@ -2269,7 +2274,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="EstaPasta_de_trabalho"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dados" sheetId="1" state="visible" r:id="rId1"/>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -462,7 +462,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -473,29 +472,31 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -843,17 +844,17 @@
   <dimension ref="B1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31.85546875" customWidth="1" style="64" min="2" max="2"/>
-    <col width="51.5703125" customWidth="1" style="50" min="3" max="3"/>
-    <col width="31.28515625" customWidth="1" style="64" min="5" max="5"/>
-    <col width="21.85546875" customWidth="1" style="64" min="6" max="6"/>
+    <col width="31.85546875" customWidth="1" style="63" min="2" max="2"/>
+    <col width="51.5703125" customWidth="1" style="67" min="3" max="3"/>
+    <col width="31.28515625" customWidth="1" style="63" min="5" max="5"/>
+    <col width="21.85546875" customWidth="1" style="63" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="2" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B2" s="25" t="inlineStr">
         <is>
           <t>proponente</t>
@@ -870,19 +871,19 @@
           <t>agencia</t>
         </is>
       </c>
-      <c r="F2" s="53" t="inlineStr">
+      <c r="F2" s="52" t="inlineStr">
         <is>
           <t>ua porto nacional (14)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B3" s="47" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>cpf/cnpj</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>32.251.489/5614-55</t>
         </is>
@@ -893,19 +894,14 @@
           <t>municipio da agencia</t>
         </is>
       </c>
-      <c r="F3" s="53" t="inlineStr">
+      <c r="F3" s="52" t="inlineStr">
         <is>
           <t>porto nacional - TO</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B4" s="48" t="inlineStr">
-        <is>
-          <t>mais de um propietario?</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
+    <row r="4" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="C4" s="67" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="33" t="inlineStr">
         <is>
@@ -916,7 +912,7 @@
         <v>38323</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B5" s="25" t="inlineStr">
         <is>
           <t>propietario</t>
@@ -932,13 +928,13 @@
           <t>municipio do cartorio</t>
         </is>
       </c>
-      <c r="F5" s="53" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>palmas - to</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B6" s="47" t="inlineStr">
         <is>
           <t>cpf/cnpj</t>
@@ -958,15 +954,8 @@
         <v>43822</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B7" s="57" t="inlineStr">
-        <is>
-          <t>mais de uma matricula?</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="63" thickBot="1"/>
+    <row r="8" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B8" s="28" t="inlineStr">
         <is>
           <t>nome do imovel</t>
@@ -986,7 +975,7 @@
         <v>42911</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B9" s="28" t="inlineStr">
         <is>
           <t>matricula</t>
@@ -1006,7 +995,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B10" s="28" t="inlineStr">
         <is>
           <t>identificação</t>
@@ -1028,7 +1017,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B11" s="28" t="inlineStr">
         <is>
           <t>area há</t>
@@ -1048,7 +1037,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B12" s="28" t="inlineStr">
         <is>
           <t>area construida</t>
@@ -1062,9 +1051,9 @@
           <t>nome</t>
         </is>
       </c>
-      <c r="F12" s="52" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="64" thickBot="1">
+      <c r="F12" s="51" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B13" s="28" t="inlineStr">
         <is>
           <t>valor de mercado</t>
@@ -1080,7 +1069,7 @@
       </c>
       <c r="F13" s="2" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B14" s="28" t="inlineStr">
         <is>
           <t>liquidação forçada</t>
@@ -1090,7 +1079,7 @@
         <v>65000000</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B15" s="28" t="inlineStr">
         <is>
           <t>car</t>
@@ -1102,7 +1091,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B16" s="28" t="inlineStr">
         <is>
           <t>gel</t>
@@ -1114,7 +1103,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B17" s="28" t="inlineStr">
         <is>
           <t>area1</t>
@@ -1124,7 +1113,7 @@
         <v>100.5205</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B18" s="28" t="inlineStr">
         <is>
           <t>area2</t>
@@ -1134,7 +1123,7 @@
         <v>321.5648</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B19" s="28" t="inlineStr">
         <is>
           <t>municipio</t>
@@ -1146,7 +1135,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="20" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B20" s="46" t="inlineStr">
         <is>
           <t>estado(uf)</t>
@@ -1158,7 +1147,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="21" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B21" s="28" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -1168,7 +1157,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="22" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B22" s="28" t="inlineStr">
         <is>
           <t>georeferenciamento</t>
@@ -1180,7 +1169,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="23" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B23" s="28" t="inlineStr">
         <is>
           <t>possui hipotecas pendentes?</t>
@@ -1192,7 +1181,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="24" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B24" s="28" t="inlineStr">
         <is>
           <t>dentro do bioma amazonico?</t>
@@ -1204,7 +1193,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="25" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B25" s="28" t="inlineStr">
         <is>
           <t>bacia</t>
@@ -1216,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="26" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B26" s="28" t="inlineStr">
         <is>
           <t>sub-bacia</t>
@@ -1263,138 +1252,138 @@
   <dimension ref="A2:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.28515625" customWidth="1" style="64" min="2" max="2"/>
-    <col width="27.7109375" customWidth="1" style="64" min="3" max="3"/>
-    <col width="20" customWidth="1" style="64" min="4" max="4"/>
-    <col width="24.140625" customWidth="1" style="64" min="5" max="5"/>
-    <col width="28.140625" customWidth="1" style="64" min="6" max="6"/>
-    <col width="18.7109375" customWidth="1" style="64" min="7" max="8"/>
-    <col width="15.85546875" customWidth="1" style="64" min="9" max="9"/>
-    <col width="20.5703125" customWidth="1" style="64" min="10" max="10"/>
-    <col width="18.140625" customWidth="1" style="64" min="11" max="12"/>
-    <col width="18.28515625" customWidth="1" style="64" min="13" max="13"/>
+    <col width="13.28515625" customWidth="1" style="63" min="2" max="2"/>
+    <col width="27.7109375" customWidth="1" style="63" min="3" max="3"/>
+    <col width="20" customWidth="1" style="63" min="4" max="4"/>
+    <col width="24.140625" customWidth="1" style="63" min="5" max="5"/>
+    <col width="28.140625" customWidth="1" style="63" min="6" max="6"/>
+    <col width="18.7109375" customWidth="1" style="63" min="7" max="8"/>
+    <col width="15.85546875" customWidth="1" style="63" min="9" max="9"/>
+    <col width="20.5703125" customWidth="1" style="63" min="10" max="10"/>
+    <col width="18.140625" customWidth="1" style="63" min="11" max="12"/>
+    <col width="18.28515625" customWidth="1" style="63" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="64" thickBot="1"/>
-    <row r="2" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A2" s="60" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="63" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>genero</t>
         </is>
       </c>
-      <c r="B2" s="55" t="inlineStr">
+      <c r="B2" s="54" t="inlineStr">
         <is>
           <t>% imovel</t>
         </is>
       </c>
-      <c r="C2" s="55" t="inlineStr">
+      <c r="C2" s="54" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="D2" s="55" t="inlineStr">
+      <c r="D2" s="54" t="inlineStr">
         <is>
           <t>cpf ou cnpj</t>
         </is>
       </c>
-      <c r="E2" s="60" t="inlineStr">
+      <c r="E2" s="58" t="inlineStr">
         <is>
           <t>casado?(a)</t>
         </is>
       </c>
-      <c r="G2" s="56" t="inlineStr">
+      <c r="G2" s="55" t="inlineStr">
         <is>
           <t>Nº matricula</t>
         </is>
       </c>
-      <c r="H2" s="56" t="inlineStr">
+      <c r="H2" s="55" t="inlineStr">
         <is>
           <t>identificacção</t>
         </is>
       </c>
-      <c r="I2" s="56" t="inlineStr">
+      <c r="I2" s="55" t="inlineStr">
         <is>
           <t>AREA HÁ</t>
         </is>
       </c>
-      <c r="J2" s="56" t="inlineStr">
+      <c r="J2" s="55" t="inlineStr">
         <is>
           <t>area contruida</t>
         </is>
       </c>
-      <c r="K2" s="56" t="inlineStr">
+      <c r="K2" s="55" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="L2" s="56" t="inlineStr">
+      <c r="L2" s="55" t="inlineStr">
         <is>
           <t>liquidação</t>
         </is>
       </c>
-      <c r="M2" s="56" t="inlineStr">
+      <c r="M2" s="55" t="inlineStr">
         <is>
           <t>CODIGO GEL</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="64" thickBot="1">
-      <c r="A3" s="53" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="63" thickBot="1">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n">
+      <c r="B3" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="52" t="inlineStr">
         <is>
           <t>miguel phelipe feitosa</t>
         </is>
       </c>
-      <c r="D3" s="58" t="inlineStr">
+      <c r="D3" s="56" t="inlineStr">
         <is>
           <t>713.254.791-79</t>
         </is>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="52" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="F3" s="52" t="inlineStr">
+      <c r="F3" s="51" t="inlineStr">
         <is>
           <t>matricula1</t>
         </is>
       </c>
-      <c r="G3" s="53" t="n">
+      <c r="G3" s="52" t="n">
         <v>1456.6547</v>
       </c>
-      <c r="H3" s="53" t="inlineStr">
+      <c r="H3" s="52" t="inlineStr">
         <is>
           <t>fazenda</t>
         </is>
       </c>
-      <c r="I3" s="53" t="n">
+      <c r="I3" s="52" t="n">
         <v>1234.5123</v>
       </c>
-      <c r="J3" s="53" t="n">
+      <c r="J3" s="52" t="n">
         <v>156.65</v>
       </c>
-      <c r="K3" s="54" t="n">
+      <c r="K3" s="53" t="n">
         <v>25000000</v>
       </c>
-      <c r="L3" s="54" t="n">
+      <c r="L3" s="53" t="n">
         <v>65000000</v>
       </c>
-      <c r="M3" s="54" t="inlineStr">
+      <c r="M3" s="53" t="inlineStr">
         <is>
           <t>c8bdfa60-64a7-4baa-83aa-d84b73759e3e</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A4" s="53" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
@@ -1402,17 +1391,17 @@
       <c r="B4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="53" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>miguel phelipe feitosa gomes</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>32.251.489/5614-55</t>
         </is>
       </c>
-      <c r="E4" s="53" t="inlineStr">
+      <c r="E4" s="52" t="inlineStr">
         <is>
           <t>não</t>
         </is>
@@ -1444,8 +1433,8 @@
       </c>
       <c r="M4" s="45" t="n"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A5" s="53" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Sra.</t>
         </is>
@@ -1461,17 +1450,17 @@
       <c r="D5" s="44" t="n">
         <v>58744</v>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>matricula3</t>
         </is>
       </c>
-      <c r="G5" s="53" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>saui</t>
         </is>
@@ -1481,253 +1470,253 @@
           <t>fazenda</t>
         </is>
       </c>
-      <c r="I5" s="53" t="inlineStr">
+      <c r="I5" s="52" t="inlineStr">
         <is>
           <t>marco</t>
         </is>
       </c>
-      <c r="J5" s="53" t="inlineStr">
+      <c r="J5" s="52" t="inlineStr">
         <is>
           <t>mara9-1</t>
         </is>
       </c>
-      <c r="K5" s="53" t="n">
+      <c r="K5" s="52" t="n">
         <v>10000</v>
       </c>
-      <c r="L5" s="53" t="n">
+      <c r="L5" s="52" t="n">
         <v>20000</v>
       </c>
-      <c r="M5" s="53" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A6" s="53" t="n"/>
+      <c r="M5" s="52" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A6" s="52" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="44" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="51" t="inlineStr">
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>matricula4</t>
         </is>
       </c>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n"/>
-      <c r="L6" s="53" t="n"/>
-      <c r="M6" s="53" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A7" s="53" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="52" t="n"/>
+      <c r="I6" s="52" t="n"/>
+      <c r="J6" s="52" t="n"/>
+      <c r="K6" s="52" t="n"/>
+      <c r="L6" s="52" t="n"/>
+      <c r="M6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A7" s="52" t="n"/>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="44" t="n"/>
-      <c r="E7" s="53" t="n"/>
-      <c r="F7" s="51" t="inlineStr">
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>matricula5</t>
         </is>
       </c>
-      <c r="G7" s="53" t="n"/>
-      <c r="H7" s="53" t="n"/>
-      <c r="I7" s="53" t="n"/>
-      <c r="J7" s="53" t="n"/>
-      <c r="K7" s="53" t="n"/>
-      <c r="L7" s="53" t="n"/>
-      <c r="M7" s="53" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A8" s="53" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="52" t="n"/>
+      <c r="I7" s="52" t="n"/>
+      <c r="J7" s="52" t="n"/>
+      <c r="K7" s="52" t="n"/>
+      <c r="L7" s="52" t="n"/>
+      <c r="M7" s="52" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A8" s="52" t="n"/>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="44" t="n"/>
       <c r="D8" s="44" t="n"/>
-      <c r="E8" s="53" t="n"/>
-      <c r="F8" s="51" t="inlineStr">
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>matricula6</t>
         </is>
       </c>
-      <c r="G8" s="53" t="n"/>
-      <c r="H8" s="53" t="n"/>
-      <c r="I8" s="53" t="n"/>
-      <c r="J8" s="53" t="n"/>
-      <c r="K8" s="53" t="n"/>
-      <c r="L8" s="53" t="n"/>
-      <c r="M8" s="53" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A9" s="53" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="52" t="n"/>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+      <c r="M8" s="52" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A9" s="52" t="n"/>
       <c r="B9" s="1" t="n"/>
       <c r="D9" s="44" t="n"/>
-      <c r="E9" s="53" t="n"/>
-      <c r="F9" s="51" t="inlineStr">
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>matricula7</t>
         </is>
       </c>
-      <c r="G9" s="53" t="n"/>
-      <c r="H9" s="53" t="n"/>
-      <c r="I9" s="53" t="n"/>
-      <c r="J9" s="53" t="n"/>
-      <c r="K9" s="53" t="n"/>
-      <c r="L9" s="53" t="n"/>
-      <c r="M9" s="53" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A10" s="53" t="n"/>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="51" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="52" t="n"/>
+      <c r="I9" s="52" t="n"/>
+      <c r="J9" s="52" t="n"/>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="52" t="n"/>
+      <c r="M9" s="52" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="51" t="n"/>
+      <c r="C10" s="50" t="n"/>
       <c r="D10" s="44" t="n"/>
-      <c r="E10" s="53" t="n"/>
-      <c r="F10" s="51" t="inlineStr">
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>matricula8</t>
         </is>
       </c>
-      <c r="G10" s="53" t="n"/>
-      <c r="H10" s="53" t="n"/>
-      <c r="I10" s="53" t="n"/>
-      <c r="J10" s="53" t="n"/>
-      <c r="K10" s="53" t="n"/>
-      <c r="L10" s="53" t="n"/>
-      <c r="M10" s="53" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A11" s="53" t="n"/>
-      <c r="B11" s="61" t="n"/>
-      <c r="C11" s="49" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="52" t="n"/>
+      <c r="I10" s="52" t="n"/>
+      <c r="J10" s="52" t="n"/>
+      <c r="K10" s="52" t="n"/>
+      <c r="L10" s="52" t="n"/>
+      <c r="M10" s="52" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="48" t="n"/>
       <c r="D11" s="44" t="n"/>
-      <c r="E11" s="53" t="n"/>
-      <c r="F11" s="51" t="inlineStr">
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>matricula9</t>
         </is>
       </c>
-      <c r="G11" s="53" t="n"/>
-      <c r="H11" s="53" t="n"/>
-      <c r="I11" s="53" t="n"/>
-      <c r="J11" s="53" t="n"/>
-      <c r="K11" s="53" t="n"/>
-      <c r="L11" s="53" t="n"/>
-      <c r="M11" s="53" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="A12" s="53" t="n"/>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="51" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="51" t="n"/>
+      <c r="C12" s="50" t="n"/>
       <c r="D12" s="44" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="51" t="inlineStr">
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>matricula10</t>
         </is>
       </c>
-      <c r="G12" s="53" t="n"/>
-      <c r="H12" s="53" t="n"/>
-      <c r="I12" s="53" t="n"/>
-      <c r="J12" s="53" t="n"/>
-      <c r="K12" s="53" t="n"/>
-      <c r="L12" s="53" t="n"/>
-      <c r="M12" s="53" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="64" thickBot="1"/>
-    <row r="14" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B14" s="55" t="inlineStr">
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="52" t="n"/>
+      <c r="K12" s="52" t="n"/>
+      <c r="L12" s="52" t="n"/>
+      <c r="M12" s="52" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="63" thickBot="1"/>
+    <row r="14" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>genero</t>
         </is>
       </c>
-      <c r="C14" s="55" t="inlineStr">
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr">
+      <c r="D14" s="54" t="inlineStr">
         <is>
           <t>cpf</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B15" s="53" t="inlineStr">
+    <row r="15" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B15" s="52" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
       </c>
-      <c r="C15" s="53" t="inlineStr">
+      <c r="C15" s="52" t="inlineStr">
         <is>
           <t>marco antonio</t>
         </is>
       </c>
-      <c r="D15" s="53" t="n">
+      <c r="D15" s="52" t="n">
         <v>9874165</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B16" s="53" t="inlineStr">
+    <row r="16" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
       </c>
-      <c r="C16" s="53" t="inlineStr">
+      <c r="C16" s="52" t="inlineStr">
         <is>
           <t>marco antonio</t>
         </is>
       </c>
-      <c r="D16" s="53" t="n">
+      <c r="D16" s="52" t="n">
         <v>9874165</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B17" s="53" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
       </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>marco antonio</t>
         </is>
       </c>
-      <c r="D17" s="53" t="n">
+      <c r="D17" s="52" t="n">
         <v>9874165</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B18" s="53" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B19" s="53" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B20" s="53" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B21" s="53" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B23" s="53" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B24" s="53" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+    <row r="18" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
@@ -1747,35 +1736,35 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.140625" customWidth="1" style="64" min="1" max="69"/>
-    <col width="9.140625" customWidth="1" style="64" min="70" max="16384"/>
+    <col width="9.140625" customWidth="1" style="63" min="1" max="70"/>
+    <col width="9.140625" customWidth="1" style="63" min="71" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="64">
-      <c r="A1" s="65" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="63">
+      <c r="A1" s="66" t="inlineStr">
         <is>
           <t>QUADRO RESUMO DA AVALIAÇÃO</t>
         </is>
       </c>
-      <c r="O1" s="66" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="64">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="O1" s="65" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="63">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>Proponente:</t>
         </is>
       </c>
-      <c r="C2" s="66" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>marco antonio feitosa</t>
         </is>
       </c>
-      <c r="J2" s="68" t="inlineStr">
+      <c r="J2" s="64" t="inlineStr">
         <is>
           <t>#486: 32.251.489/5614-55</t>
         </is>
       </c>
-      <c r="O2" s="66" t="n"/>
+      <c r="O2" s="65" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1799,24 +1788,24 @@
   <dimension ref="B2:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="61" customWidth="1" style="64" min="2" max="2"/>
-    <col width="90.85546875" customWidth="1" style="64" min="3" max="3"/>
+    <col width="61" customWidth="1" style="63" min="2" max="2"/>
+    <col width="90.85546875" customWidth="1" style="63" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="64" thickBot="1"/>
-    <row r="2" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="63" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="B2" s="19" t="inlineStr">
         <is>
           <t>DECLIVIDADE</t>
         </is>
       </c>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="C2" s="51" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="64" thickBot="1">
+    <row r="3" ht="16.5" customHeight="1" s="63" thickBot="1">
       <c r="B3" s="14" t="inlineStr">
         <is>
           <t>A - (declive igual ou inferior a 5 %):</t>
@@ -1828,7 +1817,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="64" thickBot="1">
+    <row r="4" ht="16.5" customHeight="1" s="63" thickBot="1">
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>B - (declive maior do que 5 % e igual ou menor do que 10 %):</t>
@@ -1840,7 +1829,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="64" thickBot="1">
+    <row r="5" ht="16.5" customHeight="1" s="63" thickBot="1">
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>C - (declive maior do que 10 % e igual ou menor do que 15 %):</t>
@@ -1852,7 +1841,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="64" thickBot="1">
+    <row r="6" ht="16.5" customHeight="1" s="63" thickBot="1">
       <c r="B6" s="12" t="inlineStr">
         <is>
           <t>D - (declive maior do que 15 % e igual ou menor do que 30 %):</t>
@@ -1864,7 +1853,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="64" thickBot="1">
+    <row r="7" ht="16.5" customHeight="1" s="63" thickBot="1">
       <c r="B7" s="12" t="inlineStr">
         <is>
           <t>E - (declive maior do que 30 % e igual ou menor do que 45 %):</t>
@@ -1876,7 +1865,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="64" thickBot="1">
+    <row r="8" ht="16.5" customHeight="1" s="63" thickBot="1">
       <c r="B8" s="12" t="inlineStr">
         <is>
           <t>F - (declive maior do que 45 %):</t>
@@ -1888,20 +1877,20 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="64" thickBot="1"/>
-    <row r="13" ht="15.75" customHeight="1" s="64" thickBot="1">
-      <c r="B13" s="53" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1" s="63" thickBot="1"/>
+    <row r="13" ht="15.75" customHeight="1" s="63" thickBot="1">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>PEDOLOGIA</t>
         </is>
       </c>
-      <c r="C13" s="53" t="inlineStr">
+      <c r="C13" s="52" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="14" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Afloramento Rochosos (AR)</t>
@@ -1913,7 +1902,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="15" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Argissolo Amarelo (PA)</t>
@@ -1925,7 +1914,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="16" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Argissolo Vermelho (PV)</t>
@@ -1937,7 +1926,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="17" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Argissolo vermelho-amarelo (PVA)</t>
@@ -1949,7 +1938,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="18" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Cambissolos (CX)</t>
@@ -1961,7 +1950,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="19" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Chernossolo Argilúvico (MT)</t>
@@ -1973,7 +1962,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="20" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Gleissolo háplico (GX)</t>
@@ -1985,7 +1974,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="21" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Latossolo Vermelho-Amarelo (LVA) </t>
@@ -1997,7 +1986,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="22" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Latossolo Amarelo (LA) </t>
@@ -2009,7 +1998,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="23" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Latossolo Vermelho (LV) </t>
@@ -2021,7 +2010,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="24" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Luvissolos Háplicos (TX)</t>
@@ -2033,7 +2022,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="25" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Neossolo flúvico (RY)</t>
@@ -2045,7 +2034,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="26" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Neossolos Quartzarênicos (RQ)</t>
@@ -2057,7 +2046,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="27" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Neossolos Litólicos (RL)</t>
@@ -2069,7 +2058,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="28" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Nitossolo Vermelho (NV)</t>
@@ -2081,7 +2070,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="29" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Planossolos Nátricos (SN)</t>
@@ -2093,7 +2082,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="30" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Planossolos Háplicos (SX)</t>
@@ -2105,7 +2094,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="31" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Plintossolos Pétrico (FF)</t>
@@ -2117,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="32" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Plintossolos Háplico (FX)</t>
@@ -2129,7 +2118,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="19.5" customHeight="1" s="64" thickBot="1">
+    <row r="33" ht="19.5" customHeight="1" s="63" thickBot="1">
       <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Plintossolo Argilúvico (FT)</t>
@@ -2155,13 +2144,13 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.7109375" customWidth="1" style="64" min="1" max="1"/>
-    <col width="16.85546875" customWidth="1" style="64" min="2" max="2"/>
-    <col width="14" customWidth="1" style="64" min="3" max="3"/>
-    <col width="15.42578125" customWidth="1" style="64" min="4" max="4"/>
+    <col width="19.7109375" customWidth="1" style="63" min="1" max="1"/>
+    <col width="16.85546875" customWidth="1" style="63" min="2" max="2"/>
+    <col width="14" customWidth="1" style="63" min="3" max="3"/>
+    <col width="15.42578125" customWidth="1" style="63" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="64">
+    <row r="1" ht="25.5" customHeight="1" s="63">
       <c r="A1" s="40" t="inlineStr">
         <is>
           <t>respostas memorial descritivo</t>
@@ -2240,7 +2229,7 @@
       </c>
       <c r="D4" s="1" t="n"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="64" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="63" thickBot="1">
       <c r="A5" s="44" t="inlineStr">
         <is>
           <t>CAR e Memorial</t>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="EstaPasta_de_trabalho" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\automatizar_descritivo\TEMPLATES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\automatizar_descritivo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="147">
   <si>
     <t>proponente</t>
   </si>
@@ -52,9 +52,6 @@
     <t>porto nacional - TO</t>
   </si>
   <si>
-    <t>mais de um propietario?</t>
-  </si>
-  <si>
     <t>data de solicitação</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
   </si>
   <si>
     <t>data de emissão do cartorio</t>
-  </si>
-  <si>
-    <t>mais de uma matricula?</t>
   </si>
   <si>
     <t>nome do imovel</t>
@@ -857,7 +851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -930,7 +924,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -943,7 +936,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -956,13 +948,13 @@
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1247,10 +1239,10 @@
   <dimension ref="B1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="51.5703125" style="52" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" style="62" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="62" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" style="60" customWidth="1"/>
+    <col min="3" max="3" width="51.5703125" style="51" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" style="60" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1268,7 +1260,7 @@
       <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="55" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1277,24 +1269,21 @@
         <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="55" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="60"/>
       <c r="D4" s="1"/>
       <c r="E4" s="33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="8">
         <v>38323</v>
@@ -1302,16 +1291,16 @@
     </row>
     <row r="5" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="F5" s="55" t="s">
         <v>12</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1319,30 +1308,27 @@
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>14</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>15</v>
       </c>
       <c r="F6" s="4">
         <v>43822</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="60"/>
     </row>
     <row r="8" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="27" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>19</v>
       </c>
       <c r="F8" s="4">
         <v>42911</v>
@@ -1350,73 +1336,73 @@
     </row>
     <row r="9" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="5">
         <v>1456.6547</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="F10" s="37" t="s">
         <v>24</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5">
         <v>1234.5123000000001</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="5">
         <v>156.65</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="54"/>
+        <v>29</v>
+      </c>
+      <c r="F12" s="53"/>
     </row>
     <row r="13" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="7">
         <v>25000000</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="7">
         <v>65000000</v>
@@ -1424,23 +1410,23 @@
     </row>
     <row r="15" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5">
         <v>100.5205</v>
@@ -1448,7 +1434,7 @@
     </row>
     <row r="18" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5">
         <v>321.56479999999999</v>
@@ -1456,23 +1442,23 @@
     </row>
     <row r="19" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C21" s="5">
         <v>123456</v>
@@ -1480,45 +1466,45 @@
     </row>
     <row r="22" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1541,6 +1527,36 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="492" yWindow="493" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>respostas!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>C22</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>respostas!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C23 C24 F10</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>respostas!$B$2:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>respostas!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F11</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1549,101 +1565,101 @@
   <dimension ref="B1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" style="62" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="62" customWidth="1"/>
-    <col min="4" max="4" width="20" style="62" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" style="62" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" style="62" customWidth="1"/>
-    <col min="7" max="8" width="18.7109375" style="62" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" style="62" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" style="62" customWidth="1"/>
-    <col min="11" max="12" width="18.140625" style="62" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="60" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="60" customWidth="1"/>
+    <col min="4" max="4" width="20" style="60" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" style="60" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" style="60" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" style="60" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" style="60" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" style="60" customWidth="1"/>
+    <col min="11" max="12" width="18.140625" style="60" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" style="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="H2" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="I2" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="J2" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="K2" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="L2" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="M2" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="60" t="s">
+    </row>
+    <row r="3" spans="2:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="M2" s="60" t="s">
+      <c r="C3" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="55" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="2:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="56">
+      <c r="G3" s="55">
         <v>1456.6547</v>
       </c>
-      <c r="H3" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="56">
+      <c r="H3" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="55">
         <v>1234.5123000000001</v>
       </c>
-      <c r="J3" s="56">
+      <c r="J3" s="55">
         <v>156.65</v>
       </c>
-      <c r="K3" s="58">
+      <c r="K3" s="57">
         <v>25000000</v>
       </c>
-      <c r="L3" s="58">
+      <c r="L3" s="57">
         <v>65000000</v>
       </c>
-      <c r="M3" s="58" t="s">
-        <v>38</v>
+      <c r="M3" s="57" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>67</v>
+        <v>64</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>65</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G4" s="47">
         <v>184.096</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I4" s="47">
         <v>123.0921</v>
@@ -1661,209 +1677,209 @@
     </row>
     <row r="5" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="47" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="47"/>
-      <c r="F5" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="56"/>
+      <c r="F5" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="55"/>
       <c r="H5" s="47"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
     </row>
     <row r="6" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="47"/>
-      <c r="F6" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
+      <c r="F6" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
     </row>
     <row r="7" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="47"/>
-      <c r="F7" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
+      <c r="F7" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
     </row>
     <row r="8" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="47"/>
-      <c r="F8" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
+      <c r="F8" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="47"/>
+      <c r="F9" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+    </row>
+    <row r="10" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="F9" s="57" t="s">
+      <c r="C10" s="52"/>
+      <c r="D10" s="47"/>
+      <c r="F10" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-    </row>
-    <row r="10" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="47"/>
-      <c r="F10" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
     </row>
     <row r="11" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="47"/>
+      <c r="F11" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="47"/>
-      <c r="F11" s="57" t="s">
+      <c r="C12" s="52"/>
+      <c r="D12" s="47"/>
+      <c r="F12" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-    </row>
-    <row r="12" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="47"/>
-      <c r="F12" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
     </row>
     <row r="13" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="59" t="s">
-        <v>56</v>
+      <c r="B14" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="58" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="56" t="str">
+      <c r="B15" s="55" t="str">
         <f>dados!F11</f>
         <v>Sr.</v>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="55">
         <f>dados!F12</f>
         <v>0</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="55">
         <f>dados!F13</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
     </row>
     <row r="17" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
     </row>
     <row r="18" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
     </row>
     <row r="20" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
     </row>
     <row r="21" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
     </row>
     <row r="22" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
     </row>
     <row r="23" spans="2:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
     </row>
     <row r="24" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1879,57 +1895,57 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="63" width="9.140625" style="62" customWidth="1"/>
-    <col min="64" max="16384" width="9.140625" style="62"/>
+    <col min="1" max="63" width="9.140625" style="60" customWidth="1"/>
+    <col min="64" max="16384" width="9.140625" style="60"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
+      <c r="A1" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
     </row>
     <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="65" t="str">
+      <c r="A2" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="63" t="str">
         <f>dados!C2</f>
         <v>marco antonio feitosa</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="69" t="str">
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="68" t="str">
         <f>"#486: " &amp; dados!C3</f>
         <v>#486: 713.254.791-79</v>
       </c>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="63"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1949,234 +1965,234 @@
   <dimension ref="B1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61" style="62" customWidth="1"/>
-    <col min="3" max="3" width="90.85546875" style="62" customWidth="1"/>
+    <col min="2" max="2" width="61" style="60" customWidth="1"/>
+    <col min="3" max="3" width="90.85546875" style="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>88</v>
+        <v>85</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>88</v>
+      <c r="B13" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2190,66 +2206,66 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="62" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="14" style="62" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="62" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="60" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="60" customWidth="1"/>
+    <col min="3" max="3" width="14" style="60" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="42" t="s">
         <v>142</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>

--- a/integracao.xlsx
+++ b/integracao.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="EstaPasta_de_trabalho" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\automatizar_descritivo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\automatizar_descritivo\TEMPLATES\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
@@ -133,9 +133,6 @@
     <t>TO-1718204-E7A1.2B1B.6B15.4E03.89DD.7006.7298.400E</t>
   </si>
   <si>
-    <t>gel</t>
-  </si>
-  <si>
     <t>c8bdfa60-64a7-4baa-83aa-d84b73759e3e</t>
   </si>
   <si>
@@ -289,39 +286,21 @@
     <t>DESCRIÇÃO</t>
   </si>
   <si>
-    <t>A - (declive igual ou inferior a 5 %):</t>
-  </si>
-  <si>
     <t>Compreende áreas com declives suaves, nos quais, na maior parte dos solos, o escoamento superficial é lento ou médio. O declive, por si só, não impede ou dificulta o trabalho de qualquer tipo de máquina agrícola mais usual.</t>
   </si>
   <si>
-    <t>B - (declive maior do que 5 % e igual ou menor do que 10 %):</t>
-  </si>
-  <si>
     <t>Áreas com superfícies inclinadas, geralmente com relevo ondulado, nos quais o escoamento superficial, para a maior parte dos solos, é médio ou rápido. O declive, por si só, normalmente não prejudica o uso de máquinas agrícolas.</t>
   </si>
   <si>
-    <t>C - (declive maior do que 10 % e igual ou menor do que 15 %):</t>
-  </si>
-  <si>
     <t>Compreende áreas inclinadas ou colinosas, onde o escoamento superficial é rápido na maior parte dos solos. A não ser que o declive seja muito complexo, a maior parte das máquinas agrícolas pode ser usada.</t>
   </si>
   <si>
-    <t>D - (declive maior do que 15 % e igual ou menor do que 30 %):</t>
-  </si>
-  <si>
     <t>Representada por áreas inclinadas, cujo escoamento superficial é rápido a muito rápido na maior parte dos solos. Podem ser trabalhados mecanicamente apenas em curvas de nível por máquinas simples de tração animal.</t>
   </si>
   <si>
-    <t>E - (declive maior do que 30 % e igual ou menor do que 45 %):</t>
-  </si>
-  <si>
     <t>Áreas fortemente inclinadas, cujo escoamento superficial é muito rápido. Podem ser trabalhados mecanicamente somente por máquinas simples de tração animal, assim mesmo com sérias limitações.</t>
   </si>
   <si>
-    <t>F - (declive maior do que 45 %):</t>
-  </si>
-  <si>
     <t>Constituída por áreas íngremes de regiões montanhosas, onde nenhum tipo de máquina agrícola pode trafegar. O escoamento superficial é sempre muito rápido e os solos extremamente suscetíveis à erosão hídrica.</t>
   </si>
   <si>
@@ -457,9 +436,6 @@
     <t>inserido no bioma amazonico?</t>
   </si>
   <si>
-    <t>GEL</t>
-  </si>
-  <si>
     <t>Memorial descritivo</t>
   </si>
   <si>
@@ -467,6 +443,30 @@
   </si>
   <si>
     <t>CAR</t>
+  </si>
+  <si>
+    <t>geo(codigo da parcela)</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>F - (declive maior do que 45 %)</t>
+  </si>
+  <si>
+    <t>E - (declive maior do que 30 % e igual ou menor do que 45 %)</t>
+  </si>
+  <si>
+    <t>D - (declive maior do que 15 % e igual ou menor do que 30 %)</t>
+  </si>
+  <si>
+    <t>C - (declive maior do que 10 % e igual ou menor do que 15 %)</t>
+  </si>
+  <si>
+    <t>B - (declive maior do que 5 % e igual ou menor do que 10 %)</t>
+  </si>
+  <si>
+    <t>A - (declive igual ou inferior a 5 %)</t>
   </si>
 </sst>
 </file>
@@ -851,7 +851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -941,6 +941,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1380,8 +1383,8 @@
       <c r="B12" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="5">
-        <v>156.65</v>
+      <c r="C12" s="63">
+        <v>300</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>29</v>
@@ -1418,15 +1421,15 @@
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5">
         <v>100.5205</v>
@@ -1434,7 +1437,7 @@
     </row>
     <row r="18" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="5">
         <v>321.56479999999999</v>
@@ -1442,23 +1445,23 @@
     </row>
     <row r="19" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5">
         <v>123456</v>
@@ -1466,23 +1469,23 @@
     </row>
     <row r="22" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>46</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="30" t="s">
         <v>24</v>
@@ -1490,21 +1493,21 @@
     </row>
     <row r="25" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="6"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1580,36 +1583,36 @@
     <row r="1" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="G2" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="H2" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="I2" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="J2" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="59" t="s">
+      <c r="K2" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="L2" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="M2" s="59" t="s">
         <v>60</v>
-      </c>
-      <c r="M2" s="59" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="55" t="s">
         <v>10</v>
@@ -1618,7 +1621,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3" s="55">
         <v>1456.6547</v>
@@ -1639,21 +1642,21 @@
         <v>65000000</v>
       </c>
       <c r="M3" s="57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="55" t="s">
         <v>64</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>65</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="47">
         <v>184.096</v>
@@ -1677,12 +1680,12 @@
     </row>
     <row r="5" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="47"/>
       <c r="F5" s="56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="55"/>
       <c r="H5" s="47"/>
@@ -1694,12 +1697,12 @@
     </row>
     <row r="6" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="47"/>
       <c r="F6" s="56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="55"/>
       <c r="H6" s="55"/>
@@ -1711,12 +1714,12 @@
     </row>
     <row r="7" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="47"/>
       <c r="F7" s="56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G7" s="55"/>
       <c r="H7" s="55"/>
@@ -1728,12 +1731,12 @@
     </row>
     <row r="8" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="47"/>
       <c r="F8" s="56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G8" s="55"/>
       <c r="H8" s="55"/>
@@ -1745,11 +1748,11 @@
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="47"/>
       <c r="F9" s="56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9" s="55"/>
       <c r="H9" s="55"/>
@@ -1761,12 +1764,12 @@
     </row>
     <row r="10" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="52"/>
       <c r="D10" s="47"/>
       <c r="F10" s="56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10" s="55"/>
       <c r="H10" s="55"/>
@@ -1778,12 +1781,12 @@
     </row>
     <row r="11" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="47"/>
       <c r="F11" s="56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="55"/>
       <c r="H11" s="55"/>
@@ -1795,12 +1798,12 @@
     </row>
     <row r="12" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="47"/>
       <c r="F12" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
@@ -1819,7 +1822,7 @@
         <v>29</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1900,50 +1903,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+    </row>
+    <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-    </row>
-    <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="63" t="str">
+      <c r="B2" s="65"/>
+      <c r="C2" s="64" t="str">
         <f>dados!C2</f>
         <v>marco antonio feitosa</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="68" t="str">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="69" t="str">
         <f>"#486: " &amp; dados!C3</f>
         <v>#486: 713.254.791-79</v>
       </c>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="62"/>
       <c r="O2" s="61"/>
     </row>
@@ -1972,227 +1975,227 @@
     <row r="1" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>85</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="55" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="17" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="17" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="17" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2214,38 +2217,38 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B1" s="41" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
@@ -2256,7 +2259,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -2265,7 +2268,7 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
